--- a/daily_matches/job_matches_2026-06-10.xlsx
+++ b/daily_matches/job_matches_2026-06-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Specialty AI Engineer</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, Generative AI, RAG, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f62e93765382c0b0</t>
+          <t>https://www.indeed.com/viewjob?jk=73dc6c13c1849fbd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER-REMOTE</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cdai</t>
+          <t>TrueML</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, CI/CD, Terraform, Snowflake, Databricks</t>
+          <t>Data Scientist, RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d77a89c68dff947</t>
+          <t>https://www.indeed.com/viewjob?jk=b74b9cddc3c99f92</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Emerging Tech Engineer</t>
+          <t>Platform Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Jorie AI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, Git</t>
+          <t>RAG, OpenCV, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=832dd9d49d203394</t>
+          <t>https://www.indeed.com/viewjob?jk=abff1d499014e19b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Emerging Tech Engineer</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, Git</t>
+          <t>AI Engineer, RAG, Pinecone, Prompt Engineering, BigQuery, Data Lake, Dataflow, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd7c516942bdc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0f04c8aca78a96</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Security Engineer, AI/ML</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Qualys</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Mistral, FAISS, Pinecone, TensorFlow, PyTorch, AKS, CI/CD</t>
+          <t>RAG, BigQuery, CI/CD, Git, Snowflake, BigQuery, MySQL, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d9537830b896ab5</t>
+          <t>https://www.indeed.com/viewjob?jk=5e3a3ed05ded8097</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Agent Platform</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, Keras, Kubernetes, Terraform, Git</t>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37ce7fb974562504</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4009f7a34c3ab8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kubernetes Application Support Engineer</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6983762c6333385f</t>
+          <t>https://www.indeed.com/viewjob?jk=62889aa5922edf0b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RingCentral</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kubernetes, Jenkins, Terraform, Git, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28c853894079c6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=d4cc2c66ba0e93b9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Growth</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, EC2, Terraform, Git, MySQL, Cassandra, Python, SQL, R, Java</t>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a674e49e98ceda3</t>
+          <t>https://www.indeed.com/viewjob?jk=d0092e012c75cc2a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Java springboot developer - Senior Software Engineer</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Berwyn, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c20900bb86bbe1a6</t>
+          <t>https://www.indeed.com/viewjob?jk=a414e5a1b8554cba</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Enterprise AI Product Engineer</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RingCentral</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Belmont, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Prompt Engineering, Git, PostgreSQL, MongoDB, Python, SQL, R</t>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25a8e9e63124d68</t>
+          <t>https://www.indeed.com/viewjob?jk=c3624cd7b0a14b1d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marketing Data Scientist</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Zicasso</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4157213e4eddc5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=537b772ef1ebe9ee</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Analyst - Data Engineering 5A</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java</t>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0411ee5db09b739b</t>
+          <t>https://www.indeed.com/viewjob?jk=493c0396fe981250</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Asurion</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, Docker, Kubernetes, CI/CD, GitHub Actions, Git, R, Scala, Optimization</t>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b6e8f88b93b8d2</t>
+          <t>https://www.indeed.com/viewjob?jk=d96b2c55a546723e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PSEG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a9cebe570943b9</t>
+          <t>https://www.indeed.com/viewjob?jk=3dea64f7ee5edd31</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Statistical Analyst</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=615539d002116393</t>
+          <t>https://www.indeed.com/viewjob?jk=64740ad782df5cb1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Healthfirst</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Redshift, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,42 +1056,2177 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e395311f5b80f46</t>
+          <t>https://www.indeed.com/viewjob?jk=6eeb799e5eab4148</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Certified AWS Infrastructure Architect/Landing Zone/DevOps</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f2bd983231800dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8153722997cb57af</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=082451c1b3ac524d</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b32a5cd05c4b385</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=509553f5b2b80b93</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Rochester, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4024b03d5ccdbe7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b77131ae6dad4a04</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=10a8d31d11a2ba88</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c6b64cd60eee8fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86d0f0a4bb5ca18b</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32e597607c22e457</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=165543ad99d2740a</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b070a38d68a94065</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a567d090bf66c662</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c09b7c00e3d2c83e</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb0f53deb4a9b18b</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0edf7a2d9633e5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8516e11f84de36e</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c3a7be56c01f917</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=623bb336cc90d3f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Midland, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7f04f24aa16c1bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b156cbe16df965f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b427b79fadeaeca</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3706793e6a0524a</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a90f94e3442f55d</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=479e0d19944e1a77</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21bed7e6546b8e41</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39c2bb9cf80e320f</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ff5839e147b0f9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb723b7e8b1af2fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1824380acb61d226</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cade42e913d0662e</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=019e10b76f1f876c</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31bd25bae6c274f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ddef646960a8a8d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99a403a9c1d876e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83bbe0f642103d2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3d1424b74f3dedb</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05574fa4cad0fc37</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Fresno, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac37ab0081e2642d</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a593dea989cf8f2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ba8829787244a47</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior Media Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, Glue, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c95f9149ce99f6f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Full Stack AI Product Engineer (DataEdge)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Bain &amp; Company</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4541e2bbfbff2ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer (Breakthrough)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>U.S. Venture, Inc.</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Green Bay, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Docker, Kubernetes, Terraform, Git, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b35da93de79eeb39</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Automation Test Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Qualitest</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbeea4c6d8c0cb96</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>AI/ML Software Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>GE Aerospace</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>KY, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=231e7b4c5256ee1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer (Systems Analyst III) - 26-06932</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Round Rock, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Cortex, Kubernetes, AKS, CI/CD, Git, Snowflake, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28dc0aab5e85305a</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer (Systems Analyst III) - 26-06932</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Cedar Park, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Cortex, Kubernetes, AKS, CI/CD, Git, Snowflake, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41af7ad0625ac78b</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer (Systems Analyst III) - 26-06932</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Georgetown, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Cortex, Kubernetes, AKS, CI/CD, Git, Snowflake, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47dac917810e3227</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer (Systems Analyst III) - 26-06932</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>NavitasPartners</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Cortex, Kubernetes, AKS, CI/CD, Git, Snowflake, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7fc8876e6a6ae8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer (MS Copilot)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Expleo Group</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Copilot, FastAPI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59fdb368ec33b51e</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ML Administrator</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Data Lake, CI/CD, Terraform, Git, Databricks, NoSQL, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc3940123f37f7cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior ML Engineer (ML/AI)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Lyra Health</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Docker, Kubernetes, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0710b3310b8a0f28</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Dev Ops Software Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Blue Origin</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c58a5f4d2208b676</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Data Scientist (Remote)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Corning</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Corning, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
         <v>10</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, Terraform, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87e701d86d359072</t>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Databricks, Python, R, Scala, Bayesian</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0a04565b67f1cc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer (AI Foundations)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Information Technology Senior Management Forum</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9236a1227a016f7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Edward Jones</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RAG, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35acf765e7fa8f2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Edward Jones</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RAG, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fe69692c4c1ddd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Delivery Senior Consultant, Data Engineering and Gen AI</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, Keras, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=439dfa8aa61d92ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Delivery Senior Consultant, Data Engineering and Gen AI</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, Keras, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4f55960c468b8ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Delivery Senior Consultant, Data Engineering and Gen AI</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, Keras, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a28803e8003e7823</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-10.xlsx
+++ b/daily_matches/job_matches_2026-06-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>CT_NITRO Experimental AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Qeexo, Co.</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Clemente, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, S3, Glue, Redshift, Data Lake, Docker, Apache Airflow, Git, Redshift</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Keras, Docker, AKS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30ae3ce2014da6b2</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa4878c1c49568b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Engineer (Delivery Toolkit)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, S3, FastAPI, Docker, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,89 +531,89 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73c5e09077e276bd</t>
+          <t>https://www.indeed.com/viewjob?jk=caf37a9b3156f8dd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Full Stack Engineer (Delivery Toolkit)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>First Horizon Bank</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, MLflow, CI/CD, Git, Databricks, PySpark, Tableau, Power BI, Matplotlib</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, S3, FastAPI, Docker, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93e19b901655965</t>
+          <t>https://www.indeed.com/viewjob?jk=9bcb0ad10b28a6f6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Full Stack Engineer (Delivery Toolkit)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MISO</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, S3, FastAPI, Docker, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a97da6efd240e5</t>
+          <t>https://www.indeed.com/viewjob?jk=38db06205a3e4bf5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Engineer (Delivery Toolkit)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,116 +622,116 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, BigQuery, Docker, CI/CD, Jenkins, Terraform, Git, BigQuery, Kafka</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, S3, FastAPI, Docker, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2b7127a83949ff</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b6929e731217b8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist / Machine Learning Engineer (Gen AI Focus) (contract)</t>
+          <t>Full Stack Engineer (Delivery Toolkit)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Gemini, Prompt Engineering, XGBoost, Matplotlib, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, S3, FastAPI, Docker, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d051ffe343c6b68f</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f1182f80665686</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Search Engineer</t>
+          <t>Full Stack Engineer (Delivery Toolkit)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SEMplicity</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, FastAPI, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, S3, FastAPI, Docker, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e654bb47eb17cc9a</t>
+          <t>https://www.indeed.com/viewjob?jk=1adbdb2bdac0514f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Scientist</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RedBalloon LLC</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, MLflow, Apache Airflow, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Hugging Face, Prompt Engineering, S3, Docker, Kafka, Hadoop, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43155e431f23d6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=eec78473856de0af</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Principle Data Scientist - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Hadoop, Python, SQL, R, Scala, Optimization</t>
+          <t>Copilot, Redshift, BigQuery, CI/CD, Git, Snowflake, BigQuery, Redshift, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43524ef386b91d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=295d5c0c3c32b524</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, Apache Airflow, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc750ce13952bfd8</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e8667fbc2aaf2d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software</t>
+          <t>Senior DevOps Engineer (Cloud Platform)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ensemble Health Partners</t>
+          <t>Teambuilder</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Terraform, Databricks, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a2b0700d72edef</t>
+          <t>https://www.indeed.com/viewjob?jk=b7d34ade42ca5e88</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Products)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Brillian</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -867,11 +867,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Terraform, Git, PostgreSQL, Python, SQL, R, Java, Optimization</t>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,42 +881,532 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2675163ecf3d056a</t>
+          <t>https://www.indeed.com/viewjob?jk=ac2dc57074b54ef8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Products)</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Brillian</t>
+          <t>Virtuous Software</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49f2e5c947def1cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Full Stack)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Virtuous Software</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4f4c4aef584c9a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FSO LABS - AI Developer - Senior - Bay Area</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, Kafka, Hadoop, NoSQL, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15b1ff233b5557ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Systems Analyst III</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cayuse Holdings</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Cortex, Kubernetes, AKS, CI/CD, Terraform, Git, Snowflake, Python, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2afd97da1e4e911f</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Trulieve</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Cortex, Apache Airflow, Terraform, Snowflake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86122b093407c7a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Glendale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, Kubernetes, CI/CD, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56d012e39c9d02fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FSO LABS-Kubernetes DevOps Engineer-Senior-Bay Area</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc52f1d58cea1424</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Lion Holdings</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Valuetainment</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b38caabc37c0a31a</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sr. AI Enablement Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Restaurant Brands International</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9edd09020b660c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Java Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Kafka, MongoDB, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=991dca9aba571e7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>26-1106: Full Stack Python Developer - Herndon, VA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Navitas Business Consulting</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, Databricks, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42945907e5053a04</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Systems Analyst III</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cayuse Holdings</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Cortex, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=118bece3c3bca18b</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Risk Management - AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>10</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Terraform, Git, PostgreSQL, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2c680351b7c737</t>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Docker, Kubernetes, Databricks, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb1875968106948d</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Packsize</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, Prompt Engineering, CI/CD, Databricks, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc69ee39752b2c44</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Machine Learning PhD Intern, Economics (Fall)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Instacart</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, XGBoost, Keras, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=212fc3cf0afa03b2</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-10.xlsx
+++ b/daily_matches/job_matches_2026-06-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>Software Developer Specialist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Keras, Docker, AKS</t>
+          <t>RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, OpenCV, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa4878c1c49568b</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3f1693262c6089</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Delivery Toolkit)</t>
+          <t>Senior ML Engineer / MLOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, S3, FastAPI, Docker, CI/CD, GitHub Actions, Terraform</t>
+          <t>Data Scientist, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Apache Airflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,207 +531,207 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caf37a9b3156f8dd</t>
+          <t>https://www.indeed.com/viewjob?jk=8577c851254cde7a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Delivery Toolkit)</t>
+          <t>Senior Software Engineer (API Integrations)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, S3, FastAPI, Docker, CI/CD, GitHub Actions, Terraform</t>
+          <t>RAG, Copilot, S3, Kinesis, Docker, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bcb0ad10b28a6f6</t>
+          <t>https://www.indeed.com/viewjob?jk=1badc32639c60a3b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Delivery Toolkit)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, S3, FastAPI, Docker, CI/CD, GitHub Actions, Terraform</t>
+          <t>RAG, AWS SageMaker, S3, BigQuery, Synapse, MLflow, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38db06205a3e4bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=479163dbba877015</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Delivery Toolkit)</t>
+          <t>Senior Python Engineer - Applications Development Sr Programmer Analyst - C12 - RUTHERFORD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, S3, FastAPI, Docker, CI/CD, GitHub Actions, Terraform</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Databricks, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b6929e731217b8</t>
+          <t>https://www.indeed.com/viewjob?jk=2a79fada7aa22173</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Delivery Toolkit)</t>
+          <t>Senior Python Engineer - Applications Development Sr Programmer Analyst - C12 - RUTHERFORD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, S3, FastAPI, Docker, CI/CD, GitHub Actions, Terraform</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Databricks, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f1182f80665686</t>
+          <t>https://www.indeed.com/viewjob?jk=58f9563a68281f5f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (Delivery Toolkit)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, S3, FastAPI, Docker, CI/CD, GitHub Actions, Terraform</t>
+          <t>LangChain, RAG, S3, CI/CD, PySpark, Kafka, MySQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1adbdb2bdac0514f</t>
+          <t>https://www.indeed.com/viewjob?jk=caf16b4c9308524a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>AI Infrastructure &amp; Platform Engineering Intern</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>T. Mims Corp.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Hugging Face, Prompt Engineering, S3, Docker, Kafka, Hadoop, MongoDB, Cassandra</t>
+          <t>LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec78473856de0af</t>
+          <t>https://www.indeed.com/viewjob?jk=4f49d1380e7a6bce</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lower</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Copilot, Redshift, BigQuery, CI/CD, Git, Snowflake, BigQuery, Redshift, Tableau, Power BI</t>
+          <t>AI Engineer, RAG, BigQuery, Data Lake, Dataflow, CI/CD, BigQuery, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295d5c0c3c32b524</t>
+          <t>https://www.indeed.com/viewjob?jk=65b9748ecec70c3f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R</t>
+          <t>FastAPI, Docker, Kubernetes, AKS, CI/CD, Kafka, PostgreSQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e8667fbc2aaf2d</t>
+          <t>https://www.indeed.com/viewjob?jk=f55460d0e88e7e6b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Cloud Platform)</t>
+          <t>Senior Full-Stack Software Engineer, Clinical Intelligence</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Teambuilder</t>
+          <t>MEDecision</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
+          <t>RAG, BigQuery, Docker, CI/CD, Terraform, Git, BigQuery, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7d34ade42ca5e88</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd899653b72bc10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr AI ML/Engineer - Remote Nationwide or Hybrid in MN/DC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, CI/CD, Databricks, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac2dc57074b54ef8</t>
+          <t>https://www.indeed.com/viewjob?jk=62076bebcf3f8729</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack)</t>
+          <t>Analytics Engineer, AV Safety Engineering</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Virtuous Software</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f2e5c947def1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=a4816d04cc8cc676</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack)</t>
+          <t>Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Virtuous Software</t>
+          <t>Sardine</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, BigQuery, Docker, Kubernetes, CI/CD, Snowflake, BigQuery, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f4c4aef584c9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=d08dbba9ebf8a97c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FSO LABS - AI Developer - Senior - Bay Area</t>
+          <t>Data Scientist – Strategy &amp; Analytics (Healthcare/Supply Chain)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, Kafka, Hadoop, NoSQL, Power BI, Python, SQL</t>
+          <t>Data Scientist, RAG, TensorFlow, Keras, Snowflake, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15b1ff233b5557ad</t>
+          <t>https://www.indeed.com/viewjob?jk=58e73a0dc9bab786</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Systems Analyst III</t>
+          <t>AWM-Marcus by Goldman Sachs, Marketing Analytics, Associate/Analyst Richardson, TX,</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Cortex, Kubernetes, AKS, CI/CD, Terraform, Git, Snowflake, Python, R</t>
+          <t>RAG, BigQuery, Git, Snowflake, BigQuery, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2afd97da1e4e911f</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb82b589ee61e7f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist - SCM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Trulieve</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Deerfield Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Cortex, Apache Airflow, Terraform, Snowflake, Kafka, Python, SQL, R</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Azure ML, Synapse, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86122b093407c7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=e8465d976f0e47cd</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>EMC Robotics Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, Kubernetes, CI/CD, Git, Python, SQL, R</t>
+          <t>RAG, TensorFlow, PyTorch, OpenCV, S3, CI/CD, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56d012e39c9d02fe</t>
+          <t>https://www.indeed.com/viewjob?jk=81d5f1d95f518a43</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FSO LABS-Kubernetes DevOps Engineer-Senior-Bay Area</t>
+          <t>Senior Full-Stack Developer – Provider &amp; Plan Digital</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc52f1d58cea1424</t>
+          <t>https://www.indeed.com/viewjob?jk=230e21510c5b4fcc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Lion Holdings</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Valuetainment</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, SQL, R</t>
+          <t>Gemini, TensorFlow, PyTorch, AWS SageMaker, CI/CD, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b38caabc37c0a31a</t>
+          <t>https://www.indeed.com/viewjob?jk=ce1bc8fca9deffcd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. AI Enablement Engineer</t>
+          <t>Senior Artificial Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Restaurant Brands International</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, R</t>
+          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, Git, Databricks, PySpark, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9edd09020b660c4</t>
+          <t>https://www.indeed.com/viewjob?jk=6273040b919c3115</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tyfone</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Kafka, MongoDB, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991dca9aba571e7e</t>
+          <t>https://www.indeed.com/viewjob?jk=a3493dfa91161a2c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>26-1106: Full Stack Python Developer - Herndon, VA</t>
+          <t>Cloud Solutions Architect 3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Navitas Business Consulting</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, Databricks, Python, R, Scala</t>
+          <t>RAG, Gemini, Data Lake, Docker, Kubernetes, AKS, CI/CD, Tableau, Python, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42945907e5053a04</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3ba3c7c3645334</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Systems Analyst III</t>
+          <t>Senior AI ML Engineer - Remote</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cortex, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Python, SQL, R, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Git, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118bece3c3bca18b</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac856eefa328825</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Risk Management - AI/ML Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Docker, Kubernetes, Databricks, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, MLflow, Git, Databricks, Tableau, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb1875968106948d</t>
+          <t>https://www.indeed.com/viewjob?jk=3b7b1b2565a9cff2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Packsize</t>
+          <t>Future Secure AI</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Copilot, Prompt Engineering, CI/CD, Databricks, R, Scala</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,42 +1371,847 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc69ee39752b2c44</t>
+          <t>https://www.indeed.com/viewjob?jk=8f13a73441f63c11</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Machine Learning PhD Intern, Economics (Fall)</t>
+          <t>Senior Data scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Instacart</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de0a568b86dc36f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; Systems Analyst, EHS</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Anduril</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Git, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5168af7d09678107</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; Systems Analyst, EHS</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Anduril</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ashville, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Git, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17b9a397cc4c641a</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; Systems Analyst, EHS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Anduril</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Git, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d66f56956ffe6cf9</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; Systems Analyst, EHS</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Anduril</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Git, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9b1d71ff3800610</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; Systems Analyst, EHS</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Anduril</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Git, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a49149ce709bfee</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Data Engineer - Machine Learning/AI</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Progressive</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>S3, EC2, Athena, Docker, Terraform, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee802d0b027266ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Software Engineer, Engineering Applications</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Rivian</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Copilot, FastAPI, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1752866836309783</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Sr. Analyst, Data Science</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>LPL Financial</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Fort Mill, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e231e512ae048bd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>EXL Service</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, CI/CD, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7315b26de49fefda</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>EXL Service</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, spaCy, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=422c9e1b9db56b22</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026 PhD Applied Scientist Intern (Commerce, Trust, Safety and Support), United States</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>San Francisco, CA, US USA</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D39" t="n">
         <v>10</v>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, XGBoost, Keras, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=212fc3cf0afa03b2</t>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e29484b7fe37ba5</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026 PhD Applied Scientist Intern (Commerce, Trust, Safety and Support), United States</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d25e19c5c9bcd97b</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Software Engineer - Advanced-1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Zebra Technologies</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Lincolnshire, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Jenkins, PostgreSQL, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a986359e54475df9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Software Engineer - Advanced-2</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Zebra Technologies</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Lincolnshire, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Jenkins, PostgreSQL, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00f5eb86592822c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Data Governance Analyst</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Trane Technologies</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Davidson, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Redshift, Snowflake, Redshift, Tableau, Power BI, SQL, R</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66abe43b10974b47</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>QA Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>DUETTI</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d3bbdc364a3d8fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Packsize</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, Prompt Engineering, CI/CD, Databricks, R, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46a4439d06311399</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer I</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Samsara</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Data Scientist, Data Lake, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5b478a631931283</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Covista</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Columbia, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Prompt Engineering, BigQuery, BigQuery, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3cad5bf62ae5d3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e6c8ff06287903c</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>DocuSign</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Snowflake, Tableau, Power BI, Python, SQL, R, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1424da9523c2069</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Data Analytics Data Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Solventum</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>MN, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>S3, Glue, Terraform, Snowflake, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5bfd49e1ac5c88aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>InterVenn Biosciences</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>South San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, XGBoost, LightGBM, Python, R, Bayesian</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b25e7abb6eb0cf2</t>
         </is>
       </c>
     </row>
